--- a/data/trans_camb/IP18A05-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP18A05-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 3,06</t>
+          <t>-1,68; 3,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 2,69</t>
+          <t>-1,7; 2,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 11,1</t>
+          <t>-0,85; 12,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,38</t>
+          <t>0,0; 4,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,75</t>
+          <t>0,0; 7,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,88</t>
+          <t>0,0; 15,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,14</t>
+          <t>-0,87; 2,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,79</t>
+          <t>-0,67; 2,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,01; 10,21</t>
+          <t>0,0; 9,82</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 0,0</t>
+          <t>-7,21; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 0,62</t>
+          <t>-5,91; 0,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 0,0</t>
+          <t>-6,09; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 5,02</t>
+          <t>-0,65; 4,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 4,53</t>
+          <t>-1,14; 4,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 38,83</t>
+          <t>-1,28; 38,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,4</t>
+          <t>-2,56; 1,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,6</t>
+          <t>-2,43; 1,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 20,57</t>
+          <t>-1,67; 24,76</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,87</t>
+          <t>0,0; 6,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,15</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 2,54</t>
+          <t>-0,49; 2,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,72</t>
+          <t>-0,51; 2,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 16,65</t>
+          <t>1,36; 16,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 2,06</t>
+          <t>-1,72; 2,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,3</t>
+          <t>-1,09; 3,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 7,39</t>
+          <t>-1,17; 6,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,97</t>
+          <t>-0,73; 1,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 2,39</t>
+          <t>-0,37; 2,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 9,65</t>
+          <t>0,73; 8,45</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-60,04; 1037,41</t>
+          <t>-80,81; 823,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-67,04; —</t>
+          <t>-62,06; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-39,17; —</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,66</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1556,32 +1556,32 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 0,81</t>
+          <t>-4,06; 0,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 1,59</t>
+          <t>-2,99; 1,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 0,0</t>
+          <t>-4,71; 0,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,78</t>
+          <t>-1,86; 0,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,8</t>
+          <t>-1,69; 0,93</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 0,0</t>
+          <t>-2,47; 0,0</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,58</t>
+          <t>0,0; 8,57</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,07; 8,5</t>
+          <t>1,06; 9,07</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1772,32 +1772,32 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,9</t>
+          <t>0,0; 6,01</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,95</t>
+          <t>0,0; 6,87</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,01</t>
+          <t>0,0; 47,14</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>0,0; 3,75</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,27</t>
+          <t>1,06; 6,04</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,67</t>
+          <t>0,0; 27,45</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,05</t>
+          <t>-0,62; 1,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,27</t>
+          <t>-0,46; 1,24</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,55; 6,9</t>
+          <t>0,39; 6,1</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,47</t>
+          <t>-0,29; 1,38</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,89</t>
+          <t>-0,16; 1,77</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,83; 8,04</t>
+          <t>0,77; 7,89</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,99</t>
+          <t>-0,19; 0,96</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 1,2</t>
+          <t>-0,03; 1,26</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,74</t>
+          <t>1,11; 5,66</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-68,51; 629,36</t>
+          <t>-72,01; 555,74</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-64,98; 675,61</t>
+          <t>-62,05; 658,2</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-15,01; 2435,14</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-44,38; 596,38</t>
+          <t>-38,35; 516,16</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-39,45; 644,13</t>
+          <t>-36,1; 671,65</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>24,53; 2720,99</t>
+          <t>29,52; 3208,5</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-29,43; 303,54</t>
+          <t>-30,0; 331,71</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 364,16</t>
+          <t>-11,51; 448,5</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>148,13; 1437,96</t>
+          <t>123,41; 1598,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A05-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP18A05-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 3,1</t>
+          <t>-1,69; 3,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 2,63</t>
+          <t>-1,71; 2,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 12,18</t>
+          <t>-0,97; 10,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,73</t>
+          <t>0,0; 4,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,43</t>
+          <t>0,0; 5,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,45</t>
+          <t>0,0; 15,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,21</t>
+          <t>-0,92; 2,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 2,97</t>
+          <t>-0,68; 3,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,82</t>
+          <t>0,23; 9,14</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 0,0</t>
+          <t>-6,02; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 0,58</t>
+          <t>-5,42; 0,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 0,0</t>
+          <t>-6,87; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 4,82</t>
+          <t>-0,66; 5,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 4,52</t>
+          <t>-0,94; 4,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 38,9</t>
+          <t>-1,06; 33,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,23</t>
+          <t>-2,77; 1,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,53</t>
+          <t>-2,3; 1,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 24,76</t>
+          <t>-1,79; 24,5</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,26</t>
+          <t>0,0; 6,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 2,78</t>
+          <t>-0,51; 2,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 2,77</t>
+          <t>-0,52; 2,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 16,99</t>
+          <t>1,0; 16,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 2,13</t>
+          <t>-1,55; 2,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 3,26</t>
+          <t>-1,11; 3,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 6,58</t>
+          <t>-1,09; 7,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,79</t>
+          <t>-0,5; 1,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,31</t>
+          <t>-0,33; 2,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 8,45</t>
+          <t>0,45; 8,35</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-80,81; 823,52</t>
+          <t>-55,49; 947,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-62,06; —</t>
+          <t>-66,62; 1182,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-39,17; —</t>
+          <t>-21,82; 4322,73</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1556,32 +1556,32 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 0,5</t>
+          <t>-4,07; 0,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,58</t>
+          <t>-2,95; 1,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 0,0</t>
+          <t>-4,72; 0,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,75</t>
+          <t>-1,76; 0,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,93</t>
+          <t>-1,84; 0,8</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,0</t>
+          <t>-2,59; 0,0</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,57</t>
+          <t>0,0; 7,4</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,06; 9,07</t>
+          <t>1,06; 8,88</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1772,32 +1772,32 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,01</t>
+          <t>0,0; 5,09</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,87</t>
+          <t>0,0; 6,86</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,14</t>
+          <t>0,0; 47,18</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,75</t>
+          <t>0,0; 4,73</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,06; 6,04</t>
+          <t>1,07; 6,18</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,45</t>
+          <t>0,0; 27,91</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,0</t>
+          <t>-0,55; 1,03</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,24</t>
+          <t>-0,43; 1,21</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,39; 6,1</t>
+          <t>0,32; 6,05</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,38</t>
+          <t>-0,27; 1,47</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 1,77</t>
+          <t>-0,07; 1,85</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,89</t>
+          <t>0,9; 7,49</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,96</t>
+          <t>-0,17; 0,98</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,26</t>
+          <t>-0,04; 1,3</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,66</t>
+          <t>1,26; 6,11</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-72,01; 555,74</t>
+          <t>-70,29; 704,15</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-62,05; 658,2</t>
+          <t>-53,52; 817,2</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 2435,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-38,35; 516,16</t>
+          <t>-45,22; 736,83</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-36,1; 671,65</t>
+          <t>-31,87; 888,76</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>29,52; 3208,5</t>
+          <t>31,96; 3158,27</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-30,0; 331,71</t>
+          <t>-23,93; 310,37</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 448,5</t>
+          <t>-12,28; 376,35</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>123,41; 1598,15</t>
+          <t>123,0; 1488,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A05-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP18A05-Clase-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas</t>
+          <t>Menores cuya última consulta médica fue por dispensación de recetas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,78</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,26</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,02</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,85</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,78</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,44</t>
+          <t>2,98</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,14</t>
+          <t>3,12</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 3,8</t>
+          <t>0,0; 4,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,59</t>
+          <t>0,0; 5,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 10,57</t>
+          <t>0,0; 16,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,26</t>
+          <t>-1,71; 3,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,34</t>
+          <t>-1,68; 2,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,64</t>
+          <t>-0,85; 11,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 2,16</t>
+          <t>-0,88; 2,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 3,02</t>
+          <t>-0,88; 2,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 9,14</t>
+          <t>0,0; 9,86</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>15,49%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2,13%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>340,22%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>354,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>715,32%</t>
+          <t>710,21%</t>
         </is>
       </c>
     </row>
@@ -840,34 +840,34 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,07</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,04</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,53</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-2,0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-1,43</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>-2,0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,07</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,04</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,71</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>-0,49</t>
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,33</t>
+          <t>4,84</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 0,0</t>
+          <t>-1,02; 5,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 0,59</t>
+          <t>-0,65; 4,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 0,0</t>
+          <t>-1,27; 40,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 5,36</t>
+          <t>-6,8; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 4,87</t>
+          <t>-6,08; 0,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 33,85</t>
+          <t>-7,03; 0,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,36</t>
+          <t>-2,59; 1,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 1,65</t>
+          <t>-2,6; 1,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 24,5</t>
+          <t>-1,97; 22,37</t>
         </is>
       </c>
     </row>
@@ -946,34 +946,34 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>167,23%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>162,73%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1486,23%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-71,74%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>167,23%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>162,73%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1357,92%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>-36,74%</t>
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>323,43%</t>
+          <t>360,85%</t>
         </is>
       </c>
     </row>
@@ -1056,22 +1056,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,78</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,1</t>
+          <t>0,0; 3,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1162,22 +1162,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,41</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,88</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,22</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,98</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,77</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>6,15</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,41</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,88</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>6,13</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,51</t>
+          <t>3,38</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 2,92</t>
+          <t>-1,58; 2,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 2,82</t>
+          <t>-1,14; 3,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 16,93</t>
+          <t>-1,08; 6,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 2,15</t>
+          <t>-0,41; 2,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,12</t>
+          <t>-0,57; 2,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 7,4</t>
+          <t>1,16; 16,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,94</t>
+          <t>-0,6; 1,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,4</t>
+          <t>-0,51; 2,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 8,35</t>
+          <t>0,79; 9,81</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>43,44%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>93,94%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>130,45%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>238,09%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>185,8%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1491,22%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>43,44%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>93,94%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>160,9%</t>
+          <t>1486,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>518,84%</t>
+          <t>500,37%</t>
         </is>
       </c>
     </row>
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-55,49; 947,48</t>
+          <t>-60,04; 1037,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-66,62; 1182,44</t>
+          <t>-67,04; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-21,82; 4322,73</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,87</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,32</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-1,36</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,53</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,87</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,32</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-1,36</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>-3,59; 0,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,41; 1,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,8; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 0,5</t>
+          <t>0,0; 2,66</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 1,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,79</t>
+          <t>-1,73; 0,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,8</t>
+          <t>-1,76; 0,8</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,0</t>
+          <t>-2,48; 0,0</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-63,75%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-23,69%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-63,75%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-23,69%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1704,34 +1704,34 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>0,99</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2,22</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>18,23</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>1,46</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>3,33</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>0,99</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>2,22</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>16,46</t>
-        </is>
-      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>1,19</t>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9,14</t>
+          <t>9,52</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,4</t>
+          <t>0,0; 4,9</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,06; 8,88</t>
+          <t>0,0; 6,95</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 50,88</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,09</t>
+          <t>0,0; 7,58</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,86</t>
+          <t>1,07; 8,5</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,73</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,18</t>
+          <t>1,07; 6,27</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,91</t>
+          <t>0,0; 30,4</t>
         </is>
       </c>
     </row>
@@ -1820,22 +1820,22 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1920,47 +1920,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,57</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,79</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>3,51</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>0,23</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>0,35</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>2,38</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2,37</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,41</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>0,57</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0,79</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>3,35</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,41</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0,57</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,94</t>
+          <t>3,01</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,03</t>
+          <t>-0,25; 1,47</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,21</t>
+          <t>-0,17; 1,89</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,32; 6,05</t>
+          <t>0,89; 9,11</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 1,47</t>
+          <t>-0,55; 1,05</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,85</t>
+          <t>-0,46; 1,27</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,9; 7,49</t>
+          <t>0,51; 6,9</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 0,98</t>
+          <t>-0,21; 0,99</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 1,3</t>
+          <t>-0,09; 1,2</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,26; 6,11</t>
+          <t>1,28; 5,98</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>96,49%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>133,25%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>590,28%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>41,49%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>62,72%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>430,28%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>96,49%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>133,25%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>563,19%</t>
+          <t>427,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>510,7%</t>
+          <t>524,27%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-70,29; 704,15</t>
+          <t>-44,38; 596,38</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-53,52; 817,2</t>
+          <t>-39,45; 644,13</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32,6; 3012,02</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-45,22; 736,83</t>
+          <t>-68,51; 629,36</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-31,87; 888,76</t>
+          <t>-64,98; 675,61</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>31,96; 3158,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-23,93; 310,37</t>
+          <t>-29,43; 303,54</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 376,35</t>
+          <t>-17,02; 364,16</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>123,0; 1488,97</t>
+          <t>147,91; 1513,74</t>
         </is>
       </c>
     </row>
